--- a/artfynd/A 5009-2023 artfynd.xlsx
+++ b/artfynd/A 5009-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 5009-2023 artfynd.xlsx
+++ b/artfynd/A 5009-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>82489393</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>657719.8555690602</v>
+        <v>657720</v>
       </c>
       <c r="R2" t="n">
-        <v>6640672.967972013</v>
+        <v>6640673</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +747,9 @@
           <t>2020-01-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-01-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,6 +774,112 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>82489394</v>
+      </c>
+      <c r="B3" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Funbo kyrka, 2,9 km NV-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>657701</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6640647</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2020-01-18</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2020-01-18</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
